--- a/Stock_OneClick/history/scan_result_20260526_130358.xlsx
+++ b/Stock_OneClick/history/scan_result_20260526_130358.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RawSignals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="买入观察列表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="买入历史记录" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="卖出观察列表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="卖出历史记录" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2026-05-22" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2026-05-25" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2026-05-26" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RawSignals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买入观察列表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买入历史记录" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卖出观察列表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卖出历史记录" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-22" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-25" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-26" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -634,24 +634,12 @@
       <c r="J3" s="4" t="n">
         <v>204.43</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-26; 相对D0=0.75%; 本次触发=2026-05-26(预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -703,24 +691,12 @@
       <c r="J4" s="4" t="n">
         <v>174.73</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-26; 相对D0=4.40%; 本次触发=2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -772,24 +748,12 @@
       <c r="J5" s="4" t="n">
         <v>49.445</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-26; 相对D0=2.75%; 本次触发=2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -841,24 +805,6 @@
       <c r="J6" t="n">
         <v>403.2</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-26; 相对D0=3.03%; 本次触发=2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -910,24 +856,6 @@
       <c r="J7" t="n">
         <v>1071.62</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-26; 相对D0=3.17%; 本次触发=2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -979,27 +907,9 @@
       <c r="J8" t="n">
         <v>22.61</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>D0=22.51; 最新=2026-05-26; 相对D0=0.44%; 本次触发=2026-05-26(第一买入点); 历史重复1次; 重复日期=2026-05-26</t>
+          <t>D0=22.51; 最新=2026-05-26; 相对D0=0.44%; 本次触发=2026-05-26(第一观察点); 历史重复1次; 重复日期=2026-05-26</t>
         </is>
       </c>
     </row>
@@ -1048,24 +958,12 @@
       <c r="J9" s="4" t="n">
         <v>274.47</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-26; 相对D0=4.66%; 本次触发=2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1117,24 +1015,12 @@
       <c r="J10" s="4" t="n">
         <v>13.5</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-26; 相对D0=3.69%; 本次触发=2026-05-26(预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1186,24 +1072,12 @@
       <c r="J11" s="4" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -1255,24 +1129,6 @@
       <c r="J12" t="n">
         <v>422.01</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -1324,24 +1180,12 @@
       <c r="J13" s="4" t="n">
         <v>86.5</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=86.50; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1393,24 +1237,12 @@
       <c r="J14" s="4" t="n">
         <v>108.2</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=108.20; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1462,24 +1294,6 @@
       <c r="J15" t="n">
         <v>105.85</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=105.85; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1531,24 +1345,6 @@
       <c r="J16" t="n">
         <v>88.44</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=88.44; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -1600,24 +1396,6 @@
       <c r="J17" t="n">
         <v>158.64</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=158.64; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1669,24 +1447,12 @@
       <c r="J18" s="4" t="n">
         <v>388.88</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -1738,24 +1504,12 @@
       <c r="J19" s="4" t="n">
         <v>612.34</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入)</t>
@@ -1807,27 +1561,15 @@
       <c r="J20" s="4" t="n">
         <v>68.70999999999999</v>
       </c>
-      <c r="K20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>D0=68.71; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=68.71; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1876,24 +1618,12 @@
       <c r="J21" s="4" t="n">
         <v>106.939</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -1945,27 +1675,15 @@
       <c r="J22" s="4" t="n">
         <v>12.23</v>
       </c>
-      <c r="K22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>D0=12.23; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=12.23; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -2014,24 +1732,6 @@
       <c r="J23" t="n">
         <v>84.64</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -2083,24 +1783,6 @@
       <c r="J24" t="n">
         <v>177.59</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-26; 相对D0=-2.15%</t>
@@ -2152,24 +1834,12 @@
       <c r="J25" s="4" t="n">
         <v>49.93</v>
       </c>
-      <c r="K25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-26; 相对D0=7.31%</t>
@@ -2221,24 +1891,6 @@
       <c r="J26" t="n">
         <v>15.47</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-26; 相对D0=-4.03%</t>
@@ -2290,24 +1942,12 @@
       <c r="J27" s="4" t="n">
         <v>179.16</v>
       </c>
-      <c r="K27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-26; 相对D0=-0.51%</t>
@@ -2359,24 +1999,6 @@
       <c r="J28" t="n">
         <v>136.21</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-26; 相对D0=-3.55%</t>
@@ -2428,24 +2050,12 @@
       <c r="J29" s="4" t="n">
         <v>183.55</v>
       </c>
-      <c r="K29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-26; 相对D0=2.34%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2497,24 +2107,12 @@
       <c r="J30" s="4" t="n">
         <v>307.35</v>
       </c>
-      <c r="K30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-26; 相对D0=-5.76%</t>
@@ -2566,24 +2164,12 @@
       <c r="J31" s="4" t="n">
         <v>240.35</v>
       </c>
-      <c r="K31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-26; 相对D0=3.60%</t>
@@ -2635,24 +2221,6 @@
       <c r="J32" t="n">
         <v>131.21</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-26; 相对D0=0.54%</t>
@@ -2704,24 +2272,12 @@
       <c r="J33" s="4" t="n">
         <v>84.92</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-26; 相对D0=-0.59%</t>
@@ -2773,24 +2329,12 @@
       <c r="J34" s="4" t="n">
         <v>433.59</v>
       </c>
-      <c r="K34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-26; 相对D0=1.78%</t>
@@ -2842,24 +2386,12 @@
       <c r="J35" s="4" t="n">
         <v>18.43</v>
       </c>
-      <c r="K35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>D0=18.43; 最新=2026-05-26; 相对D0=0.00%</t>
@@ -2910,24 +2442,6 @@
       </c>
       <c r="J36" t="n">
         <v>324.03</v>
-      </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3165,24 +2679,12 @@
       <c r="J48" s="4" t="n">
         <v>90.64</v>
       </c>
-      <c r="K48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出 | 预警卖出)</t>
@@ -3234,24 +2736,12 @@
       <c r="J49" s="4" t="n">
         <v>184.71</v>
       </c>
-      <c r="K49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3303,24 +2793,12 @@
       <c r="J50" s="4" t="n">
         <v>136.21</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>D0=136.21; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3372,24 +2850,12 @@
       <c r="J51" s="4" t="n">
         <v>37.515</v>
       </c>
-      <c r="K51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>D0=37.52; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出 | 预警卖出)</t>
@@ -3441,24 +2907,12 @@
       <c r="J52" s="4" t="n">
         <v>307.35</v>
       </c>
-      <c r="K52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3510,24 +2964,12 @@
       <c r="J53" s="4" t="n">
         <v>57.46</v>
       </c>
-      <c r="K53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3579,24 +3021,12 @@
       <c r="J54" s="4" t="n">
         <v>13.35</v>
       </c>
-      <c r="K54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3648,24 +3078,12 @@
       <c r="J55" s="4" t="n">
         <v>41.07</v>
       </c>
-      <c r="K55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-26; 相对D0=-0.96%</t>
@@ -3762,7 +3180,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4578,8 +3995,6 @@
       <c r="T9" t="b">
         <v>0</v>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=47.33; 4H分金=53.85</t>
@@ -4922,8 +4337,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.01; 4H分金=60.23</t>
@@ -5005,8 +4418,6 @@
       <c r="T14" t="b">
         <v>0</v>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=45.83; 4H分金=49.45</t>
@@ -5784,8 +5195,6 @@
       <c r="T23" t="b">
         <v>0</v>
       </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=45.22; 4H分金=56.96</t>
@@ -6302,8 +5711,6 @@
       <c r="T29" t="b">
         <v>1</v>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=40.99; 4H分金=34.86</t>
@@ -6513,7 +5920,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6774,7 +6181,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -7383,7 +6790,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7777,8 +7184,6 @@
       <c r="T46" t="b">
         <v>0</v>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=47.14; 4H分金=53.35</t>
@@ -7937,7 +7342,6 @@
       <c r="D2" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46164</v>
       </c>
@@ -7989,7 +7393,6 @@
       <c r="D3" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46164</v>
       </c>
@@ -8095,7 +7498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8323,7 +7726,6 @@
       <c r="G7" s="12" t="n">
         <v>-0.040323</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -8423,7 +7825,6 @@
       <c r="G10" s="12" t="n">
         <v>-0.035477</v>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -8631,7 +8032,6 @@
       <c r="G16" s="13" t="n">
         <v>0.035991</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8663,7 +8063,6 @@
       <c r="G17" s="13" t="n">
         <v>0.005441</v>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -8763,7 +8162,6 @@
       <c r="G20" s="13" t="n">
         <v>0.017793</v>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -9011,11 +8409,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9027,7 +8420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9188,24 +8581,12 @@
       <c r="J3" s="4" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9257,24 +8638,12 @@
       <c r="J4" s="4" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9326,24 +8695,12 @@
       <c r="J5" s="4" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9395,24 +8752,12 @@
       <c r="J6" s="4" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9464,24 +8809,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9533,24 +8860,12 @@
       <c r="J8" s="4" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9602,24 +8917,12 @@
       <c r="J9" s="4" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9671,24 +8974,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9740,24 +9025,12 @@
       <c r="J11" s="4" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9809,24 +9082,12 @@
       <c r="J12" s="4" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9878,24 +9139,12 @@
       <c r="J13" s="4" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9947,24 +9196,12 @@
       <c r="J14" s="4" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10016,24 +9253,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10085,24 +9304,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10154,24 +9355,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10223,24 +9406,12 @@
       <c r="J18" s="4" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10292,24 +9463,12 @@
       <c r="J19" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10361,24 +9520,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10430,24 +9571,12 @@
       <c r="J21" s="4" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10684,24 +9813,12 @@
       <c r="J33" s="4" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10746,11 +9863,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10762,7 +9874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -10862,7 +9974,6 @@
       <c r="E4" t="n">
         <v>422.01</v>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -10940,7 +10051,6 @@
       <c r="E7" t="n">
         <v>105.85</v>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -11064,7 +10174,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -11116,7 +10226,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -11148,7 +10258,6 @@
       <c r="E15" t="n">
         <v>84.64</v>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -11200,7 +10309,6 @@
       <c r="E17" t="n">
         <v>324.03</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18"/>
     <row r="19">
@@ -11604,7 +10712,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
